--- a/reservas_salon.xlsx
+++ b/reservas_salon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henri\OneDrive\Escritorio\CEUTEC\Ingenieria_de_software_II\ExamenI_IngenieriaSoftwareII_HildaMelendez_62151194\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6061FC2-457B-4D30-8546-7D713FCBC566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EA503D-A55B-44E7-B164-11C60C60C757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,131 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Teléfono</t>
+  </si>
+  <si>
+    <t>Camila Gisel Rodriguez Hernandez</t>
+  </si>
+  <si>
+    <t>camila.rodriguez@example.com</t>
+  </si>
+  <si>
+    <t>1122-3344</t>
+  </si>
+  <si>
+    <t>Daniela Fernanda Torres Morales</t>
+  </si>
+  <si>
+    <t>daniela.torres@example.com</t>
+  </si>
+  <si>
+    <t>9988-7766</t>
+  </si>
+  <si>
+    <t>Lucía Sofia Fernández Matamoros</t>
+  </si>
+  <si>
+    <t>lucia.fernandez@example.com</t>
+  </si>
+  <si>
+    <t>7744-2211</t>
+  </si>
+  <si>
+    <t>Greicy Valentina  Cruz Estrada</t>
+  </si>
+  <si>
+    <t>Greicy.cruz@example.com</t>
+  </si>
+  <si>
+    <t>3366-8899</t>
+  </si>
+  <si>
+    <t>Isabela Nohemi Martinez Lopez</t>
+  </si>
+  <si>
+    <t>IsabelaMartinez@gmail.com</t>
+  </si>
+  <si>
+    <t>6644-3322</t>
+  </si>
+  <si>
+    <t>Antonella Elizabeth Rios Guevara</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> antonella.rios@example.com</t>
+  </si>
+  <si>
+    <t>2266-4411</t>
+  </si>
+  <si>
+    <t>Mariana Lizeth Guzman Hernandez</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> mariana.guzman@example.com</t>
+  </si>
+  <si>
+    <t>8866-5500</t>
+  </si>
+  <si>
+    <t>ID Cliente</t>
+  </si>
+  <si>
+    <t>Servicio</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Manicure</t>
+  </si>
+  <si>
+    <t>2025-05-25 02:00 PM</t>
+  </si>
+  <si>
+    <t>Confirmada</t>
+  </si>
+  <si>
+    <t>Coloración</t>
+  </si>
+  <si>
+    <t>2025-05-25 10:00 AM</t>
+  </si>
+  <si>
+    <t>2025-05-27 01:00 PM</t>
+  </si>
+  <si>
+    <t>Corte de Cabello</t>
+  </si>
+  <si>
+    <t>2025-05-26 02:00 PM</t>
+  </si>
+  <si>
+    <t>2025-05-27 10:00 AM</t>
+  </si>
+  <si>
+    <t>2025-05-25 06:00 PM</t>
+  </si>
+  <si>
+    <t>Pedicure</t>
+  </si>
+  <si>
+    <t>2025-05-27 09:00 AM</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -359,18 +483,299 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>